--- a/output/北塩原村_打合せ記録_20261009.xlsx
+++ b/output/北塩原村_打合せ記録_20261009.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_裏づけの状況" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_読み取れなかったところ" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_追加の照会事項" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_補足資料の確認" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +51,13 @@
       <name val="游ゴシック"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +104,11 @@
         <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BFBFBF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -125,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -161,6 +172,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -528,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -706,15 +721,32 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>補足資料</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>手帳と受給者証の整理（本文31段落・表4点・画像3点）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>同日受領。05シートで確認した。確かめられたこと5件／使う前に直すところ7件</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>追加の照会事項</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>6件</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>村M-28〜M-31、熊谷氏S-15・S-16</t>
         </is>
@@ -1789,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1987,7 +2019,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05シート J6 の続き（利用者負担上限額についての結論）、及び9月30日を基準日とする典拠</t>
+          <t>【J6の続きは解決】補足資料「手帳と受給者証の整理」（同日受領）の画像2・画像3により、児・者の負担上限月額が判明した。残るのは9月30日を基準日とする典拠</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2009,30 +2041,62 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
+          <t>S-17</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>熊谷氏</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>補足資料の画像1（対象疾患一覧130疾患）を最新の一覧（令和7年4月から376疾病）に差し替えること。あわせて表2（大人が所持できる手帳）の写し誤りと、「区分が3以上」がどの区分を指すかの確認</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>130疾患は施行当初の数であり、240疾病以上が抜ける。計画又は試算に用いると対象者を取りこぼす</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>補足資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>S-16</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>熊谷氏</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>読み取りに迷った4語（解除／協力雇用主／サービス料／学術規定）の意図</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>記録の正確さを保つ</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>読み取り</t>
         </is>
@@ -2045,4 +2109,357 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>補足資料「手帳と受給者証の整理」の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>同日に受領した補足資料（本文31段落・表4点・画像3点）の確認結果です。画像は厚生労働省の資料の写しであり、数値は画像から目で読み取っています（機械照合はできません）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>確かめられたこと</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>出所</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>当方の受け止め</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>受給者証は1人で最大3枚になりうる</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>本文（表3）</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>児童福祉法のサービス（受給者証・児童用）、障害者総合支援法のサービス（受給者証・総合用）、地域生活支援事業の移動支援（Ａ4の紙の場合あり）がそれぞれ別に発行される。身体手帳と療育手帳を併せ持つ児童で区分が一定以上の場合、2枚目が加わる</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>当方が第1回レビューで是正した「全国共通の受給者証区分という区分体系は存在しない」という整理と整合し、さらに具体的。支給決定者数を数えるときは、3つの制度をまたいで延べと実人数が食い違う点に注意が要る（U-7・M-19に直結）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>障がい児の負担上限月額</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>画像2（厚生労働省の資料の写し）</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>生活保護 0円／低所得（市町村民税非課税世帯）0円／一般1（市町村民税課税世帯・所得割28万円未満）通所施設・ホームヘルプ4,600円、入所施設 9,300円／一般2（上記以外）37,200円。注：収入が概ね890万円以下の世帯が一般1の対象</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>J6セルで切れていた「児の場合、親の課税状況により、利用負担上限額が（」の続きがこれにあたる（S-15の解決）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>障がい者の負担上限月額</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>画像3（厚生労働省の資料の写し）</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>生活保護 0円／低所得 0円／一般1（市町村民税課税世帯・所得割16万円未満。入所施設利用者（20歳以上）とグループホーム利用者を除く）9,300円／一般2（上記以外）37,200円。注1：3人世帯で障害基礎年金1級受給の場合は収入が概ね300万円以下。注2：所得割16万円は収入が概ね670万円以下。注3：入所施設利用者（20歳以上）とグループホーム利用者は市町村民税課税世帯の場合「一般2」</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>入所施設利用者とグループホーム利用者の扱いが異なる点は、施設入所支援4人（第4章（１））と共同生活援助の見込量を扱ううえで押さえておく</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>手帳を軸にしたコーディネートは相談支援専門員の役割</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>障がい者では療育手帳と精神保健福祉手帳の両方、あるいは身体・精神・療育のすべてを所持する方もいる。どの手帳を軸に支援するかを調整するのが相談支援専門員</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>第5章8の相談支援の供給制約（M-20）の裏づけになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>指定難病は手帳がなくても対象になりうる</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>本文・画像1</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>指定難病の対象疾患に該当すると、手帳がなくても障がい福祉サービスの対象になる可能性がある</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>手帳所持者数だけで対象者を数えると漏れる。第2章2（手帳所持者数）と第5章1（推計方法）の両方に関わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>■ 使う前に直す必要があるところ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>重さ</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>何が起きているか</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>画像1 対象疾患一覧が130疾患</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>施行当初（平成25年4月）の数と思われる。障害者総合支援法の対象疾病は、令和6年4月から369疾病、令和7年4月から376疾病に拡大されている</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>240疾病以上が抜けるため、この一覧を計画又は試算に用いると対象者を取りこぼす。最新の一覧に差し替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>表2「大人が所持できる手帳」の写し誤り</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>療育手帳の欄が「児童福祉法のサービス利用可能（児童デイなど）」のままになっている（表1からの写し）。精神保健福祉手帳の欄が空。「※療育が必要な児童という判定」の行が大人の表に残っている</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>大人は児童デイを利用できない。表2を作り直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>手帳の種類と根拠法の対応</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>表1・表2は「身体手帳→総合支援法」「療育手帳→児童福祉法」と対応させているが、障害児通所支援（児童福祉法）の利用は手帳の有無を要件とせず、障害者総合支援法のサービスも児童が利用できる。手帳の種別で根拠法が分かれるわけではない</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>実務上の傾向を書いたものと読んだが、見込量の算定根拠にすると誤る。本村の実態に即して書き直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>「区分が3以上の場合」の区分</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>18歳未満は障害支援区分の認定を行わない。短期入所は障害児支援区分1〜3、居宅介護等は5領域11項目の調査による</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>どの区分を指すかを熊谷氏に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>相談支援専門員の担当件数</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>「介護保険と異なり、相談員1人当たりの担当者数は決まっていません」とあるが、法令上の上限がない一方、報酬上は取扱件数40件以上で基本報酬が逓減する仕組みがある</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>M-20（相談支援の体制）の照会を、逓減を踏まえた聞き方に直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>他団体の例</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>特定の市の相談員の担当件数が例として挙げられている</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>本件の成果品では「他団体」と匿名化する（令和8年の取り決め）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>「公認心理士」は「公認心理師」、「障碍者」は本計画では「障がい者」。「これば」「いたうされた」は誤記と読んだ</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>本計画に取り込む際に揃える</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/北塩原村_打合せ記録_20261009.xlsx
+++ b/output/北塩原村_打合せ記録_20261009.xlsx
@@ -57,7 +57,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -109,8 +109,13 @@
         <fgColor rgb="00BFBFBF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -132,11 +137,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -178,6 +227,14 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -743,7 +800,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>8件</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1821,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2051,17 +2108,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>補足資料の画像1（対象疾患一覧130疾患）を最新の一覧（令和7年4月から376疾病）に差し替えること。あわせて表2（大人が所持できる手帳）の写し誤りと、「区分が3以上」がどの区分を指すかの確認</t>
+          <t>【一覧は入手済み】令和8年10月9日に厚生労働省の資料を受領し、376疾病の一覧（令和7年4月1日適用）を確認した。残るのは表2（大人が所持できる手帳）の写し誤りの是正と、「区分が3以上」がどの区分を指すかの確認</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>130疾患は施行当初の数であり、240疾病以上が抜ける。計画又は試算に用いると対象者を取りこぼす</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>最優先</t>
+          <t>130疾患は施行当初の数であり、246疾病が抜ける。計画又は試算に用いると対象者を取りこぼす</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -2073,30 +2130,62 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
+          <t>S-18</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>村・熊谷氏</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>計画に「難病等（令和7年4月から376疾病）も障がい福祉サービスの対象である」旨を書くか。書く場合、第２章２（手帳所持者数）に手帳を所持しない対象者がいることを注記し、第５章１（推計方法）で対象者の数え方を整理する</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>当方の素案・他メンバー版のいずれも「難病」の語が0件。手帳所持者数だけで対象者を数えると、手帳を所持しない難病等の方が漏れる</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>補足資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
           <t>S-16</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>熊谷氏</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>読み取りに迷った4語（解除／協力雇用主／サービス料／学術規定）の意図</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>記録の正確さを保つ</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>読み取り</t>
         </is>
@@ -2117,7 +2206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2314,12 +2403,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>施行当初（平成25年4月）の数と思われる。障害者総合支援法の対象疾病は、令和6年4月から369疾病、令和7年4月から376疾病に拡大されている</t>
+          <t>【原典で確認済み】厚生労働省「障害者総合支援法の対象疾病（難病等）の見直しについて」（令和8年10月9日に受領。source/制度資料/）により、130疾病は平成25年4月の施行時の数であることを確認した。その後7次にわたる見直しを経て、令和7年4月1日から376疾病</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>240疾病以上が抜けるため、この一覧を計画又は試算に用いると対象者を取りこぼす。最新の一覧に差し替える</t>
+          <t>246疾病が抜けるため、この一覧を計画又は試算に用いると対象者を取りこぼす。原典 p5〜p7 の一覧（376疾病）に差し替える</t>
         </is>
       </c>
     </row>
@@ -2455,9 +2544,346 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>■ 対象疾病の見直しの経過（厚生労働省の資料から。原典照合済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>疾病数</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>平成25年４月</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>施行時</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>130疾病</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>難病患者等居宅生活支援事業の対象疾病と同じ範囲で開始</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>平成27年１月</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>第１次見直し</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>130 ⇒ 151疾病</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>平成27年７月</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>第２次見直し</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>151 ⇒ 332疾病</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>平成29年４月</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>第３次見直し</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>332 ⇒ 358疾病</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>平成30年４月</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>第４次見直し</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>358 ⇒ 359疾病</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>令和元年７月</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>第５次見直し</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>359 ⇒ 361疾病</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>令和３年11月</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>第６次見直し</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>361 ⇒ 366疾病</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>令和６年４月</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>第７次見直し</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>366 ⇒ 369疾病</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>令和７年４月１日</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>告示改正により適用</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>369 ⇒ 376疾病</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>令和6年11月5日の第10回障害者総合支援法対象疾病検討会で方針。新たに対象となる疾病7、表記が変更された疾病2、障害者総合支援法独自の対象疾病29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>■ 対象疾病の要件（指定難病の要件との違い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>指定難病の要件</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>障害者総合支援法での取扱い</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>① 発病の機構が明らかでない</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>要件としない</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>② 治療方法が確立していない</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>要件とする</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>③ 患者数が人口の0.1％程度に達しない</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>要件としない</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>④ 長期の療養を必要とするもの</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>要件とする</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>⑤ 診断に関し客観的な指標による一定の基準が定まっていること</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>要件とする</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>※ 他の施策体系が樹立している疾病を除く。疾病の「重症度」は勘案しない。手帳を所持していなくても、対象疾病に該当すれば障がい福祉サービスの対象になりうる（障害者総合支援法第4条第1項）。本村の計画は、当方の素案・他メンバー版のいずれも「難病」の語が0件であり、手帳所持者数だけで対象者を示している。</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="18" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/北塩原村_打合せ記録_20261009.xlsx
+++ b/output/北塩原村_打合せ記録_20261009.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -795,15 +795,32 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>制度資料</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>対象疾病の見直し（7頁）と障害支援区分認定マニュアル（56頁）</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月9日受領。source/制度資料/ に格納。見直しの経過9件・要件5件・実務6件を原典照合して05シートに記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>追加の照会事項</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>8件</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>9件</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>村M-28〜M-31、熊谷氏S-15・S-16</t>
         </is>
@@ -1878,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2130,27 +2147,27 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>S-18</t>
+          <t>M-33</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>村・熊谷氏</t>
+          <t>村</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>計画に「難病等（令和7年4月から376疾病）も障がい福祉サービスの対象である」旨を書くか。書く場合、第２章２（手帳所持者数）に手帳を所持しない対象者がいることを注記し、第５章１（推計方法）で対象者の数え方を整理する</t>
+          <t>難病患者等の障害支援区分認定の体制。①認定調査員に保健師・看護師等を充てられるか（委託している場合は委託先）②市町村審査会は単独か共同設置か、専門医の関与と委員研修の有無③「難病患者等の状態について（様式例）」を用いているか</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>当方の素案・他メンバー版のいずれも「難病」の語が0件。手帳所持者数だけで対象者を数えると、手帳を所持しない難病等の方が漏れる</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>障害支援区分認定マニュアル（令和7年4月）は、難病患者等の認定調査に医療の専門知識を求め、審査会には専門医の参加や委員研修が必要という意見を載せている。本村の体制で対応できるかを確かめる</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2162,30 +2179,62 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>S-18</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>村・熊谷氏</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>計画に「難病等（令和7年4月から376疾病）も障がい福祉サービスの対象である」旨を書くか。書く場合、第２章２（手帳所持者数）に手帳を所持しない対象者がいることを注記し、第５章１（推計方法）で対象者の数え方を整理する</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>当方の素案・他メンバー版のいずれも「難病」の語が0件。手帳所持者数だけで対象者を数えると、手帳を所持しない難病等の方が漏れる</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>補足資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>S-16</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>熊谷氏</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>読み取りに迷った4語（解除／協力雇用主／サービス料／学術規定）の意図</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>記録の正確さを保つ</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>読み取り</t>
         </is>
@@ -2206,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2870,21 +2919,182 @@
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
     </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>■ 障害支援区分認定マニュアル（令和7年4月・56頁）から本村の実務に関わるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>原典の頁</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>本村への含意</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>指定難病と障害者総合支援法の対象疾病の範囲</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>p30</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>指定難病（医療費助成の対象）は令和7年4月現在348疾病。障害者総合支援法の対象疾病は376疾病であり、28疾病多い。同法は患者数による限定を行わず、重症度も勘案しない</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>医療費助成の対象外でも障がい福祉サービスの対象になりうる。「指定難病の受給者証の有無」で対象者を数えると漏れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>難病患者等の障害者手帳の取得状況</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>p35</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>難病患者等でも手帳を取得できるが、身体障害者手帳の所有率は疾病により幅がある（平成22年度。亜急性硬化性全脳炎87.5％、網膜色素変性症55.6％、筋萎縮性側索硬化症53.2％、肺動脈性肺高血圧症41.1％ほか）</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>手帳を持たない方が半数近くに上る疾病もある。第2章2（手帳所持者数）だけで対象者を示すと実態と離れる（S-18）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>症状の変化が難病の特徴であること</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>p33</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>平成22年度の調査（1,380人）で、症状の変化は「毎日ある」41.2％、「日によって変化が大きい」27.8％、「進行している」19.1％、「大きな周期で良くなったり悪くなったりする」12.0％</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>見込量を月平均の実利用者数だけで置くと、症状が重いときに必要な量が落ちる。推計方法（必要量と確保できる量の区別）に関わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>認定調査の留意点</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>p38・p39</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>認定調査員は保健師・看護師など医療に関する専門的な知識を有する者が望まれ、他の資格の場合は保健所の保健師等の同行が望ましい。調査は長時間にしない。「できる・できない」ではなく、日常生活で困っていること・動作に要する時間・症状が悪いときに実際どうしているかを確認する。症状が変化する場合は「より重度な状態（支援を最も必要とする状態）」を詳細に聞き取る</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>本村の認定調査の体制（保健師の関与、委託先）を確認する必要がある（M-33）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>市町村審査会の審査判定</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>p50</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>二次判定は「できない状況（最も支援が必要な状態）」を想定して行う。障害支援区分の有効期間は3年が基本だが、症状の進行が見込まれる場合は有効期間について市町村に報告する。症状が変化する場合はサービスに関する意見を付す。委員の研修や専門医の参加が必要という意見がある</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>本村の審査会が単独か共同設置かにより、専門医の関与と委員研修の手当ての仕方が変わる（M-33）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>様式例</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>p52・p53</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>「難病患者等の状態について（様式例）」と医師意見書の記載例がある。通常の特記事項の様式では記載が困難な場合に用いる</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>村が難病患者等の支給決定を行う際にそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>※ 他の施策体系が樹立している疾病を除く。疾病の「重症度」は勘案しない。手帳を所持していなくても、対象疾病に該当すれば障がい福祉サービスの対象になりうる（障害者総合支援法第4条第1項）。本村の計画は、当方の素案・他メンバー版のいずれも「難病」の語が0件であり、手帳所持者数だけで対象者を示している。</t>
         </is>
       </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="17" t="n"/>
-      <c r="D41" s="18" t="n"/>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A51:D51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/北塩原村_打合せ記録_20261009.xlsx
+++ b/output/北塩原村_打合せ記録_20261009.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>①現行計画の基準日との接続の可否を確認する ②9月30日とする理由の典拠を熊谷氏に確認する ③村に9月30日時点のデータが取れるかを照会する（M-28）</t>
+          <t>①現行計画の基準日との接続の可否を確認する ②9月30日とする理由の典拠を熊谷氏に確認する ③村に9月30日時点のデータが取れるかを照会する（Ｍ-28）</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>①こども・子育て計画の推計の元データと基準月を村に照会する（M-29） ②介護保険事業計画が用いる人口とも揃える（K-8） ③3つの人口系列のどれを正本にするかを決める</t>
+          <t>①こども・子育て計画の推計の元データと基準月を村に照会する（Ｍ-29） ②介護保険事業計画が用いる人口とも揃える（K-8） ③3つの人口系列のどれを正本にするかを決める</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>当方の照会（M-19ほか）は数値そのものを求める書き方にしていたが、台帳の有無と抽出の可否を先に尋ねる方が村の負担が軽く、回答も早いと考えられる。照会文の書き方をこの形に揃える。</t>
+          <t>当方の照会（Ｍ-19ほか）は数値そのものを求める書き方にしていたが、台帳の有無と抽出の可否を先に尋ねる方が村の負担が軽く、回答も早いと考えられる。照会文の書き方をこの形に揃える。</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>村への照会文（S-4・M-19）を「台帳で把握できるか」から入る形に書き換える</t>
+          <t>村への照会文（Ｓ-4・Ｍ-19）を「台帳で把握できるか」から入る形に書き換える</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>①村に職場適応訓練の実施実績の有無を照会する（M-30） ②任意事業に加える場合の財源を確認する ③素案 第5章14（関係機関との連携）に障害者職業センター・ハローワークとの連携として先に書く</t>
+          <t>①村に職場適応訓練の実施実績の有無を照会する（Ｍ-30） ②任意事業に加える場合の財源を確認する ③素案 第5章14（関係機関との連携）に障害者職業センター・ハローワークとの連携として先に書く</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>①区分6・重度訪問介護1名を置く場合の書き方（根拠の1文）を当方で起案する ②地域生活支援事業・社協の事業で補う範囲を村・社協に確認する（M-31） ③素案 第5章4の内数の表に反映する</t>
+          <t>①区分6・重度訪問介護1名を置く場合の書き方（根拠の1文）を当方で起案する ②地域生活支援事業・社協の事業で補う範囲を村・社協に確認する（Ｍ-31） ③素案 第5章4の内数の表に反映する</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>U-6。村に照会する（M-30）</t>
+          <t>U-6。村に照会する（Ｍ-30）</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>U-2。村に照会する（M-29）</t>
+          <t>U-2。村に照会する（Ｍ-29）</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>J6セルで切れていた「児の場合、親の課税状況により、利用負担上限額が（」の続きがこれにあたる（S-15の解決）</t>
+          <t>J6セルで切れていた「児の場合、親の課税状況により、利用負担上限額が（」の続きがこれにあたる（Ｓ-15の解決）</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>第5章8の相談支援の供給制約（M-20）の裏づけになる</t>
+          <t>第5章8の相談支援の供給制約（Ｍ-20）の裏づけになる</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>手帳を持たない方が半数近くに上る疾病もある。第2章2（手帳所持者数）だけで対象者を示すと実態と離れる（S-18）</t>
+          <t>手帳を持たない方が半数近くに上る疾病もある。第2章2（手帳所持者数）だけで対象者を示すと実態と離れる（Ｓ-18）</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>本村の認定調査の体制（保健師の関与、委託先）を確認する必要がある（M-33）</t>
+          <t>本村の認定調査の体制（保健師の関与、委託先）を確認する必要がある（Ｍ-33）</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>本村の審査会が単独か共同設置かにより、専門医の関与と委員研修の手当ての仕方が変わる（M-33）</t>
+          <t>本村の審査会が単独か共同設置かにより、専門医の関与と委員研修の手当ての仕方が変わる（Ｍ-33）</t>
         </is>
       </c>
     </row>
